--- a/Project 1.xlsx
+++ b/Project 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Esso\Excel course\Project 1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281D3E1B-CB5C-4C2D-AD81-1EED60811233}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{653E526E-E8ED-4321-9473-F5363B294745}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,15 +22,31 @@
   </sheets>
   <definedNames>
     <definedName name="_xlcn.WorksheetConnection_Project1.xlsxTable11" hidden="1">Table1[]</definedName>
+    <definedName name="Slicer_Customer">#N/A</definedName>
+    <definedName name="Slicer_Total">#N/A</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="42" r:id="rId7"/>
-    <pivotCache cacheId="45" r:id="rId8"/>
-    <pivotCache cacheId="96" r:id="rId9"/>
-    <pivotCache cacheId="99" r:id="rId10"/>
+    <pivotCache cacheId="49" r:id="rId7"/>
+    <pivotCache cacheId="51" r:id="rId8"/>
+    <pivotCache cacheId="53" r:id="rId9"/>
+    <pivotCache cacheId="56" r:id="rId10"/>
   </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
+      <x14:pivotCaches>
+        <pivotCache cacheId="8" r:id="rId11"/>
+      </x14:pivotCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId12"/>
+        <x14:slicerCache r:id="rId13"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -81,7 +97,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="79">
   <si>
     <t>Order ID</t>
   </si>
@@ -316,6 +332,9 @@
   <si>
     <t>Apr</t>
   </si>
+  <si>
+    <t>Fashion Sales Analysis Dashboard</t>
+  </si>
 </sst>
 </file>
 
@@ -324,10 +343,10 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="169" formatCode="_([$EGP]\ * #,##0_);_([$EGP]\ * \(#,##0\);_([$EGP]\ * &quot;-&quot;?_);_(@_)"/>
-    <numFmt numFmtId="172" formatCode="_([$EGP]\ * #,##0_);_([$EGP]\ * \(#,##0\);_([$EGP]\ * &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_([$EGP]\ * #,##0_);_([$EGP]\ * \(#,##0\);_([$EGP]\ * &quot;-&quot;?_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_([$EGP]\ * #,##0_);_([$EGP]\ * \(#,##0\);_([$EGP]\ * &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -357,8 +376,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,8 +404,14 @@
         <bgColor theme="9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -380,11 +419,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -398,18 +446,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -419,11 +464,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="27">
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
@@ -431,27 +482,22 @@
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="172" formatCode="_([$EGP]\ * #,##0_);_([$EGP]\ * \(#,##0\);_([$EGP]\ * &quot;-&quot;??_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="_([$EGP]\ * #,##0_);_([$EGP]\ * \(#,##0\);_([$EGP]\ * &quot;-&quot;?_);_(@_)"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="0.0"/>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -480,6 +526,29 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="167" formatCode="_([$EGP]\ * #,##0_);_([$EGP]\ * \(#,##0\);_([$EGP]\ * &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_([$EGP]\ * #,##0_);_([$EGP]\ * \(#,##0\);_([$EGP]\ * &quot;-&quot;?_);_(@_)"/>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0"/>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -629,19 +698,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1785,19 +1842,7 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -3092,13 +3137,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
                   </a:schemeClr>
                 </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
@@ -3124,13 +3175,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -3144,35 +3201,119 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
           <c:symbol val="circle"/>
           <c:size val="6"/>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
         </c:marker>
         <c:dLbl>
@@ -3191,131 +3332,11 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3359,20 +3380,42 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:alpha val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -3390,9 +3433,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1"/>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -3417,9 +3462,9 @@
                   <c:spPr>
                     <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="50000"/>
-                          <a:lumOff val="50000"/>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
                         </a:schemeClr>
                       </a:solidFill>
                     </a:ln>
@@ -3479,7 +3524,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="65"/>
+        <c:gapWidth val="100"/>
+        <c:overlap val="-24"/>
         <c:axId val="983208160"/>
         <c:axId val="983208576"/>
       </c:barChart>
@@ -3496,11 +3542,11 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="75000"/>
-                <a:lumOff val="25000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -3512,11 +3558,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -3539,29 +3584,17 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="95000"/>
-                      <a:lumOff val="5000"/>
-                      <a:alpha val="42000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="0">
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="75000"/>
-                      <a:alpha val="36000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -3571,6 +3604,32 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
         <c:crossAx val="983208160"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
@@ -3598,30 +3657,25 @@
     <a:gradFill flip="none" rotWithShape="1">
       <a:gsLst>
         <a:gs pos="0">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="39000">
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
         </a:gs>
         <a:gs pos="100000">
-          <a:schemeClr val="lt1">
-            <a:lumMod val="75000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
           </a:schemeClr>
         </a:gs>
       </a:gsLst>
       <a:path path="circle">
-        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
       </a:path>
       <a:tileRect/>
     </a:gradFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="25000"/>
-          <a:lumOff val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -3683,13 +3737,19 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="95000"/>
                   </a:schemeClr>
                 </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
                 <a:cs typeface="+mn-cs"/>
@@ -3702,14 +3762,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.34914235305649033"/>
-          <c:y val="0.11472003499562555"/>
-        </c:manualLayout>
-      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -3723,13 +3775,19 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
                 </a:schemeClr>
               </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
               <a:latin typeface="+mn-lt"/>
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
@@ -3743,35 +3801,119 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:dLblPos val="inEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="diamond"/>
+          <c:size val="5"/>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
         </c:marker>
         <c:dLbl>
@@ -3790,131 +3932,11 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="inEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1">
-              <a:alpha val="85000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="lt1">
-                <a:alpha val="50000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1"/>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -3958,20 +3980,42 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1">
-                <a:alpha val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:alpha val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
@@ -3989,9 +4033,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="lt1"/>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
                     </a:solidFill>
                     <a:latin typeface="+mn-lt"/>
                     <a:ea typeface="+mn-ea"/>
@@ -4016,9 +4062,9 @@
                   <c:spPr>
                     <a:ln w="9525">
                       <a:solidFill>
-                        <a:schemeClr val="dk1">
-                          <a:lumMod val="50000"/>
-                          <a:lumOff val="50000"/>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
                         </a:schemeClr>
                       </a:solidFill>
                     </a:ln>
@@ -4090,7 +4136,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="65"/>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
         <c:axId val="305349872"/>
         <c:axId val="305350288"/>
       </c:barChart>
@@ -4107,11 +4154,11 @@
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
-          <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="dk1">
-                <a:lumMod val="75000"/>
-                <a:lumOff val="25000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -4123,11 +4170,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" baseline="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -4155,24 +4201,12 @@
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:gradFill>
-                <a:gsLst>
-                  <a:gs pos="100000">
-                    <a:schemeClr val="dk1">
-                      <a:lumMod val="95000"/>
-                      <a:lumOff val="5000"/>
-                      <a:alpha val="42000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                  <a:gs pos="0">
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="75000"/>
-                      <a:alpha val="36000"/>
-                    </a:schemeClr>
-                  </a:gs>
-                </a:gsLst>
-                <a:lin ang="5400000" scaled="0"/>
-              </a:gradFill>
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -4196,9 +4230,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="dk1">
-                    <a:lumMod val="75000"/>
-                    <a:lumOff val="25000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -4225,12 +4258,7 @@
       <c:legendPos val="r"/>
       <c:overlay val="0"/>
       <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="39000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:noFill/>
         <a:ln>
           <a:noFill/>
         </a:ln>
@@ -4243,9 +4271,8 @@
           <a:pPr>
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -4272,30 +4299,25 @@
     <a:gradFill flip="none" rotWithShape="1">
       <a:gsLst>
         <a:gs pos="0">
-          <a:schemeClr val="lt1"/>
-        </a:gs>
-        <a:gs pos="39000">
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
         </a:gs>
         <a:gs pos="100000">
-          <a:schemeClr val="lt1">
-            <a:lumMod val="75000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
           </a:schemeClr>
         </a:gs>
       </a:gsLst>
       <a:path path="circle">
-        <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
       </a:path>
       <a:tileRect/>
     </a:gradFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="25000"/>
-          <a:lumOff val="75000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
+    <a:ln>
+      <a:noFill/>
     </a:ln>
     <a:effectLst/>
   </c:spPr>
@@ -4422,122 +4444,8 @@
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln w="34925" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -4551,122 +4459,8 @@
       </c:pivotFmt>
       <c:pivotFmt>
         <c:idx val="1"/>
-        <c:spPr>
-          <a:gradFill rotWithShape="1">
-            <a:gsLst>
-              <a:gs pos="0">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="103000"/>
-                  <a:lumMod val="102000"/>
-                  <a:tint val="94000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="50000">
-                <a:schemeClr val="accent1">
-                  <a:satMod val="110000"/>
-                  <a:lumMod val="100000"/>
-                  <a:shade val="100000"/>
-                </a:schemeClr>
-              </a:gs>
-              <a:gs pos="100000">
-                <a:schemeClr val="accent1">
-                  <a:lumMod val="99000"/>
-                  <a:satMod val="120000"/>
-                  <a:shade val="78000"/>
-                </a:schemeClr>
-              </a:gs>
-            </a:gsLst>
-            <a:lin ang="5400000" scaled="0"/>
-          </a:gradFill>
-          <a:ln w="34925" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
-        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="lt1">
-                      <a:lumMod val="85000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -5330,8 +5124,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -5374,6 +5167,211 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -5435,6 +5433,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-497E-4C5F-8443-96631A26A770}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -5477,6 +5480,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-497E-4C5F-8443-96631A26A770}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -5519,6 +5527,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-497E-4C5F-8443-96631A26A770}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -5561,6 +5574,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-497E-4C5F-8443-96631A26A770}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
@@ -5603,6 +5621,11 @@
                 </a:outerShdw>
               </a:effectLst>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-497E-4C5F-8443-96631A26A770}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:spPr>
@@ -8285,41 +8308,39 @@
 </file>
 
 <file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="205">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="209">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea>
     <cs:lnRef idx="0"/>
@@ -8332,149 +8353,113 @@
       <a:gradFill flip="none" rotWithShape="1">
         <a:gsLst>
           <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="39000">
-            <a:schemeClr val="lt1"/>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
           </a:gs>
           <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="75000"/>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
             </a:schemeClr>
           </a:gs>
         </a:gsLst>
         <a:path path="circle">
-          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
         </a:path>
         <a:tileRect/>
       </a:gradFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-          <a:alpha val="75000"/>
-        </a:schemeClr>
+        <a:schemeClr val="lt1"/>
       </a:solidFill>
     </cs:spPr>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="31750" cap="rnd">
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:alpha val="85000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
   <cs:dataPointMarkerLayout symbol="circle" size="6"/>
@@ -8482,10 +8467,10 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -8501,17 +8486,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -8523,20 +8507,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -8547,14 +8531,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:prstDash val="dash"/>
@@ -8566,14 +8550,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8585,7 +8568,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -8593,28 +8576,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
@@ -8624,28 +8595,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -8654,14 +8613,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:prstDash val="dash"/>
@@ -8673,14 +8632,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -8691,19 +8650,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="95000"/>
-          <a:alpha val="39000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
   <cs:plotArea>
@@ -8711,7 +8661,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -8719,7 +8669,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -8727,17 +8677,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8750,14 +8699,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -8769,12 +8718,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -8783,7 +8739,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -8798,9 +8754,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -8810,7 +8765,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -8818,9 +8773,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -8831,16 +8786,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -8848,48 +8797,46 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="218">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="222">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200" cap="all" baseline="0"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea>
     <cs:lnRef idx="0"/>
@@ -8902,160 +8849,124 @@
       <a:gradFill flip="none" rotWithShape="1">
         <a:gsLst>
           <a:gs pos="0">
-            <a:schemeClr val="lt1"/>
-          </a:gs>
-          <a:gs pos="39000">
-            <a:schemeClr val="lt1"/>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
           </a:gs>
           <a:gs pos="100000">
-            <a:schemeClr val="lt1">
-              <a:lumMod val="75000"/>
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
             </a:schemeClr>
           </a:gs>
         </a:gsLst>
         <a:path path="circle">
-          <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
         </a:path>
         <a:tileRect/>
       </a:gradFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
-    </cs:fontRef>
-    <cs:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:dataLabel>
   <cs:dataLabelCallout>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="lt1"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-          <a:alpha val="75000"/>
-        </a:schemeClr>
+        <a:schemeClr val="lt1"/>
       </a:solidFill>
     </cs:spPr>
-    <cs:defRPr sz="900" b="1" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
       <a:spAutoFit/>
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:alpha val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="31750" cap="rnd">
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:alpha val="85000"/>
-          </a:schemeClr>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="phClr">
-          <a:alpha val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointMarkerLayout size="5"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -9071,17 +8982,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -9093,20 +9003,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="50000"/>
-          <a:lumOff val="50000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -9117,14 +9027,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:prstDash val="dash"/>
@@ -9136,14 +9046,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9155,7 +9064,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
@@ -9163,28 +9072,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
@@ -9194,28 +9091,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="100000">
-              <a:schemeClr val="dk1">
-                <a:lumMod val="95000"/>
-                <a:lumOff val="5000"/>
-                <a:alpha val="42000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="0">
-              <a:schemeClr val="lt1">
-                <a:lumMod val="75000"/>
-                <a:alpha val="36000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:gridlineMinor>
@@ -9224,14 +9109,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:prstDash val="dash"/>
@@ -9243,14 +9128,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -9261,19 +9146,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1">
-          <a:lumMod val="95000"/>
-          <a:alpha val="39000"/>
-        </a:schemeClr>
-      </a:solidFill>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
   <cs:plotArea>
@@ -9281,7 +9157,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D>
@@ -9289,7 +9165,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -9297,17 +9173,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="31750" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9320,14 +9195,14 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -9339,12 +9214,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1800" b="1" kern="1200" baseline="0"/>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -9353,7 +9235,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="19050" cap="rnd">
@@ -9368,9 +9250,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -9380,7 +9261,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -9388,9 +9269,9 @@
       </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -9401,16 +9282,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:valueAxis>
   <cs:wall>
@@ -9418,7 +9293,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
@@ -10467,7 +10342,7 @@
             </a:ln>
           </xdr:spPr>
           <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="27432" rIns="27432" bIns="27432" anchor="ctr" upright="1"/>
+            <a:bodyPr vertOverflow="clip" wrap="square" lIns="27432" tIns="22860" rIns="27432" bIns="22860" anchor="ctr" upright="1"/>
             <a:lstStyle/>
             <a:p>
               <a:pPr algn="ctr" rtl="0">
@@ -10514,7 +10389,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9B1F888-C99C-433D-8785-32322F63B51F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10555,7 +10430,7 @@
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B43D16C0-EEAD-494D-B93B-6FCCC3289CF3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10596,7 +10471,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67DEFE04-BFB3-499D-B718-0E93CED47523}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10622,22 +10497,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>312962</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>77561</xdr:rowOff>
+      <xdr:colOff>494805</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76323</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>5441</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>153761</xdr:rowOff>
+      <xdr:colOff>309254</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>86591</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D15309A0-5773-400B-BFA6-F775E39842AA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10660,22 +10535,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>13607</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>68036</xdr:rowOff>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>56903</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>318407</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>144236</xdr:rowOff>
+      <xdr:colOff>519545</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>98961</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9AA310F-4DC8-43E5-A971-93FCCD212752}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10698,22 +10573,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>27215</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>63954</xdr:rowOff>
+      <xdr:colOff>259772</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>69272</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>332015</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>140154</xdr:rowOff>
+      <xdr:colOff>598715</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>98962</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="4" name="Chart 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D898EFCC-1EA4-4FFA-BBD6-FA0D9F2F4220}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000004000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10736,22 +10611,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>326573</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>593766</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="5" name="Chart 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A83ECB11-AA82-4FAC-8628-7254D632BC9F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000005000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10769,6 +10644,162 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>591540</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>48615</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>601931</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>160565</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="23" name="Customer">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0AD6F8A-48C2-4AC0-A8E1-C3418B95BB49}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Customer"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9915182842" y="728972"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>597724</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>166131</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>1979</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>92528</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="24" name="Total">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E76D2DC7-3F3A-4880-AB1A-E24A20369FD0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Total"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9915176658" y="3444215"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -10794,7 +10825,7 @@
         <xdr:cNvPr id="3" name="Chart 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A22E1B14-5B00-4443-A422-A968ED9480A7}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000003000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10816,9 +10847,179 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="mohamed elzaghal" refreshedDate="45869.424270254633" backgroundQuery="1" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{81886ECD-DE87-48CC-9F39-A574602A1595}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="mohamed elzaghal" refreshedDate="45871.143708449075" backgroundQuery="1" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{09CD201E-B904-411F-9FC9-FC593550B88B}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="2">
+  <cacheFields count="3">
+    <cacheField name="[Table1].[Category].[Category]" caption="Category" numFmtId="0" hierarchy="4" level="1">
+      <sharedItems count="3">
+        <s v="Accessories"/>
+        <s v="Clothing"/>
+        <s v="Footwear"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Sum of Total]" caption="Sum of Total" numFmtId="0" hierarchy="21" level="32767"/>
+    <cacheField name="[Table1].[Customer].[Customer]" caption="Customer" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="22">
+    <cacheHierarchy uniqueName="[Table1].[Order ID]" caption="Order ID" attribute="1" defaultMemberUniqueName="[Table1].[Order ID].[All]" allUniqueName="[Table1].[Order ID].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Customer]" caption="Customer" attribute="1" defaultMemberUniqueName="[Table1].[Customer].[All]" allUniqueName="[Table1].[Customer].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Region]" caption="Region" attribute="1" defaultMemberUniqueName="[Table1].[Region].[All]" allUniqueName="[Table1].[Region].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Table1].[Product].[All]" allUniqueName="[Table1].[Product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[Table1].[Category].[All]" allUniqueName="[Table1].[Category].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Quantity]" caption="Quantity" attribute="1" defaultMemberUniqueName="[Table1].[Quantity].[All]" allUniqueName="[Table1].[Quantity].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Unit Price]" caption="Unit Price" attribute="1" defaultMemberUniqueName="[Table1].[Unit Price].[All]" allUniqueName="[Table1].[Unit Price].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Total]" caption="Total" attribute="1" defaultMemberUniqueName="[Table1].[Total].[All]" allUniqueName="[Table1].[Total].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date]" caption="Order Date" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Order Date].[All]" allUniqueName="[Table1].[Order Date].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Sales Rep]" caption="Sales Rep" attribute="1" defaultMemberUniqueName="[Table1].[Sales Rep].[All]" allUniqueName="[Table1].[Sales Rep].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Total2]" caption="Total2" attribute="1" defaultMemberUniqueName="[Table1].[Total2].[All]" allUniqueName="[Table1].[Total2].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Table1].[Month].[All]" allUniqueName="[Table1].[Month].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Table1].[Year].[All]" allUniqueName="[Table1].[Year].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Target]" caption="Target" attribute="1" defaultMemberUniqueName="[Table1].[Target].[All]" allUniqueName="[Table1].[Target].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date (Year)]" caption="Order Date (Year)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Year)].[All]" allUniqueName="[Table1].[Order Date (Year)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date (Quarter)]" caption="Order Date (Quarter)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Quarter)].[All]" allUniqueName="[Table1].[Order Date (Quarter)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date (Month)]" caption="Order Date (Month)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Month)].[All]" allUniqueName="[Table1].[Order Date (Month)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date (Month Index)]" caption="Order Date (Month Index)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Month Index)].[All]" allUniqueName="[Table1].[Order Date (Month Index)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Quantity]" caption="Sum of Quantity" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="5"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Total]" caption="Sum of Total" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="7"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="mohamed elzaghal" refreshedDate="45871.143709027776" backgroundQuery="1" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{BFA525EC-1F04-4BCF-92AE-E2F1315D5C75}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
+    <cacheField name="[Table1].[Product].[Product]" caption="Product" numFmtId="0" hierarchy="3" level="1">
+      <sharedItems count="5">
+        <s v="Dress"/>
+        <s v="Hat"/>
+        <s v="Jacket"/>
+        <s v="Scarf"/>
+        <s v="Sneakers"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="[Measures].[Sum of Quantity]" caption="Sum of Quantity" numFmtId="0" hierarchy="20" level="32767"/>
+    <cacheField name="[Table1].[Customer].[Customer]" caption="Customer" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="22">
+    <cacheHierarchy uniqueName="[Table1].[Order ID]" caption="Order ID" attribute="1" defaultMemberUniqueName="[Table1].[Order ID].[All]" allUniqueName="[Table1].[Order ID].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Customer]" caption="Customer" attribute="1" defaultMemberUniqueName="[Table1].[Customer].[All]" allUniqueName="[Table1].[Customer].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Region]" caption="Region" attribute="1" defaultMemberUniqueName="[Table1].[Region].[All]" allUniqueName="[Table1].[Region].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Table1].[Product].[All]" allUniqueName="[Table1].[Product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[Table1].[Category].[All]" allUniqueName="[Table1].[Category].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Quantity]" caption="Quantity" attribute="1" defaultMemberUniqueName="[Table1].[Quantity].[All]" allUniqueName="[Table1].[Quantity].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Unit Price]" caption="Unit Price" attribute="1" defaultMemberUniqueName="[Table1].[Unit Price].[All]" allUniqueName="[Table1].[Unit Price].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Total]" caption="Total" attribute="1" defaultMemberUniqueName="[Table1].[Total].[All]" allUniqueName="[Table1].[Total].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date]" caption="Order Date" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Order Date].[All]" allUniqueName="[Table1].[Order Date].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Sales Rep]" caption="Sales Rep" attribute="1" defaultMemberUniqueName="[Table1].[Sales Rep].[All]" allUniqueName="[Table1].[Sales Rep].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Total2]" caption="Total2" attribute="1" defaultMemberUniqueName="[Table1].[Total2].[All]" allUniqueName="[Table1].[Total2].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Table1].[Month].[All]" allUniqueName="[Table1].[Month].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Table1].[Year].[All]" allUniqueName="[Table1].[Year].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Target]" caption="Target" attribute="1" defaultMemberUniqueName="[Table1].[Target].[All]" allUniqueName="[Table1].[Target].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date (Year)]" caption="Order Date (Year)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Year)].[All]" allUniqueName="[Table1].[Order Date (Year)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date (Quarter)]" caption="Order Date (Quarter)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Quarter)].[All]" allUniqueName="[Table1].[Order Date (Quarter)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date (Month)]" caption="Order Date (Month)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Month)].[All]" allUniqueName="[Table1].[Order Date (Month)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date (Month Index)]" caption="Order Date (Month Index)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Month Index)].[All]" allUniqueName="[Table1].[Order Date (Month Index)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Quantity]" caption="Sum of Quantity" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="5"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Total]" caption="Sum of Total" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="7"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Table1" caption="Table1"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="mohamed elzaghal" refreshedDate="45871.143709490738" backgroundQuery="1" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{81886ECD-DE87-48CC-9F39-A574602A1595}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="3">
     <cacheField name="[Table1].[Sales Rep].[Sales Rep]" caption="Sales Rep" numFmtId="0" hierarchy="9" level="1">
       <sharedItems count="5">
         <s v="Ali"/>
@@ -10829,10 +11030,18 @@
       </sharedItems>
     </cacheField>
     <cacheField name="[Measures].[Sum of Total]" caption="Sum of Total" numFmtId="0" hierarchy="21" level="32767"/>
+    <cacheField name="[Table1].[Customer].[Customer]" caption="Customer" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
   </cacheFields>
   <cacheHierarchies count="22">
     <cacheHierarchy uniqueName="[Table1].[Order ID]" caption="Order ID" attribute="1" defaultMemberUniqueName="[Table1].[Order ID].[All]" allUniqueName="[Table1].[Order ID].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Customer]" caption="Customer" attribute="1" defaultMemberUniqueName="[Table1].[Customer].[All]" allUniqueName="[Table1].[Customer].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Customer]" caption="Customer" attribute="1" defaultMemberUniqueName="[Table1].[Customer].[All]" allUniqueName="[Table1].[Customer].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+    </cacheHierarchy>
     <cacheHierarchy uniqueName="[Table1].[Region]" caption="Region" attribute="1" defaultMemberUniqueName="[Table1].[Region].[All]" allUniqueName="[Table1].[Region].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Table1].[Product].[All]" allUniqueName="[Table1].[Product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[Table1].[Category].[All]" allUniqueName="[Table1].[Category].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
@@ -10893,86 +11102,10 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="mohamed elzaghal" refreshedDate="45869.42427152778" backgroundQuery="1" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{09CD201E-B904-411F-9FC9-FC593550B88B}">
+<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="mohamed elzaghal" refreshedDate="45871.143710069446" backgroundQuery="1" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9583E334-979F-486B-9AA3-DCE000B0770F}">
   <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="2">
-    <cacheField name="[Table1].[Category].[Category]" caption="Category" numFmtId="0" hierarchy="4" level="1">
-      <sharedItems count="3">
-        <s v="Accessories"/>
-        <s v="Clothing"/>
-        <s v="Footwear"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Sum of Total]" caption="Sum of Total" numFmtId="0" hierarchy="21" level="32767"/>
-  </cacheFields>
-  <cacheHierarchies count="22">
-    <cacheHierarchy uniqueName="[Table1].[Order ID]" caption="Order ID" attribute="1" defaultMemberUniqueName="[Table1].[Order ID].[All]" allUniqueName="[Table1].[Order ID].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Customer]" caption="Customer" attribute="1" defaultMemberUniqueName="[Table1].[Customer].[All]" allUniqueName="[Table1].[Customer].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Region]" caption="Region" attribute="1" defaultMemberUniqueName="[Table1].[Region].[All]" allUniqueName="[Table1].[Region].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Table1].[Product].[All]" allUniqueName="[Table1].[Product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[Table1].[Category].[All]" allUniqueName="[Table1].[Category].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Quantity]" caption="Quantity" attribute="1" defaultMemberUniqueName="[Table1].[Quantity].[All]" allUniqueName="[Table1].[Quantity].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Unit Price]" caption="Unit Price" attribute="1" defaultMemberUniqueName="[Table1].[Unit Price].[All]" allUniqueName="[Table1].[Unit Price].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Total]" caption="Total" attribute="1" defaultMemberUniqueName="[Table1].[Total].[All]" allUniqueName="[Table1].[Total].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Order Date]" caption="Order Date" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Order Date].[All]" allUniqueName="[Table1].[Order Date].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Sales Rep]" caption="Sales Rep" attribute="1" defaultMemberUniqueName="[Table1].[Sales Rep].[All]" allUniqueName="[Table1].[Sales Rep].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Total2]" caption="Total2" attribute="1" defaultMemberUniqueName="[Table1].[Total2].[All]" allUniqueName="[Table1].[Total2].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Table1].[Month].[All]" allUniqueName="[Table1].[Month].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Table1].[Year].[All]" allUniqueName="[Table1].[Year].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Target]" caption="Target" attribute="1" defaultMemberUniqueName="[Table1].[Target].[All]" allUniqueName="[Table1].[Target].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Order Date (Year)]" caption="Order Date (Year)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Year)].[All]" allUniqueName="[Table1].[Order Date (Year)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Order Date (Quarter)]" caption="Order Date (Quarter)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Quarter)].[All]" allUniqueName="[Table1].[Order Date (Quarter)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Order Date (Month)]" caption="Order Date (Month)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Month)].[All]" allUniqueName="[Table1].[Order Date (Month)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Order Date (Month Index)]" caption="Order Date (Month Index)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Month Index)].[All]" allUniqueName="[Table1].[Order Date (Month Index)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Quantity]" caption="Sum of Quantity" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="5"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Total]" caption="Sum of Total" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="7"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table1" caption="Table1"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="mohamed elzaghal" refreshedDate="45869.426089004628" backgroundQuery="1" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{9583E334-979F-486B-9AA3-DCE000B0770F}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="5">
+  <cacheFields count="6">
     <cacheField name="[Table1].[Order Date].[Order Date]" caption="Order Date" numFmtId="0" hierarchy="8" level="1">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2025-05-30T00:00:00" maxDate="2026-07-31T00:00:00" count="15">
         <d v="2025-05-30T00:00:00"/>
@@ -11017,27 +11150,35 @@
       </sharedItems>
     </cacheField>
     <cacheField name="[Measures].[Sum of Total]" caption="Sum of Total" numFmtId="0" hierarchy="21" level="32767"/>
+    <cacheField name="[Table1].[Customer].[Customer]" caption="Customer" numFmtId="0" hierarchy="1" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
   </cacheFields>
   <cacheHierarchies count="22">
-    <cacheHierarchy uniqueName="[Table1].[Order ID]" caption="Order ID" attribute="1" defaultMemberUniqueName="[Table1].[Order ID].[All]" allUniqueName="[Table1].[Order ID].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Customer]" caption="Customer" attribute="1" defaultMemberUniqueName="[Table1].[Customer].[All]" allUniqueName="[Table1].[Customer].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Region]" caption="Region" attribute="1" defaultMemberUniqueName="[Table1].[Region].[All]" allUniqueName="[Table1].[Region].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Table1].[Product].[All]" allUniqueName="[Table1].[Product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[Table1].[Category].[All]" allUniqueName="[Table1].[Category].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Quantity]" caption="Quantity" attribute="1" defaultMemberUniqueName="[Table1].[Quantity].[All]" allUniqueName="[Table1].[Quantity].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Unit Price]" caption="Unit Price" attribute="1" defaultMemberUniqueName="[Table1].[Unit Price].[All]" allUniqueName="[Table1].[Unit Price].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Total]" caption="Total" attribute="1" defaultMemberUniqueName="[Table1].[Total].[All]" allUniqueName="[Table1].[Total].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Order ID]" caption="Order ID" attribute="1" defaultMemberUniqueName="[Table1].[Order ID].[All]" allUniqueName="[Table1].[Order ID].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Customer]" caption="Customer" attribute="1" defaultMemberUniqueName="[Table1].[Customer].[All]" allUniqueName="[Table1].[Customer].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="5"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Region]" caption="Region" attribute="1" defaultMemberUniqueName="[Table1].[Region].[All]" allUniqueName="[Table1].[Region].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Table1].[Product].[All]" allUniqueName="[Table1].[Product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[Table1].[Category].[All]" allUniqueName="[Table1].[Category].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Quantity]" caption="Quantity" attribute="1" defaultMemberUniqueName="[Table1].[Quantity].[All]" allUniqueName="[Table1].[Quantity].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Unit Price]" caption="Unit Price" attribute="1" defaultMemberUniqueName="[Table1].[Unit Price].[All]" allUniqueName="[Table1].[Unit Price].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Total]" caption="Total" attribute="1" defaultMemberUniqueName="[Table1].[Total].[All]" allUniqueName="[Table1].[Total].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Order Date]" caption="Order Date" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Order Date].[All]" allUniqueName="[Table1].[Order Date].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="7" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
         <fieldUsage x="0"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Sales Rep]" caption="Sales Rep" attribute="1" defaultMemberUniqueName="[Table1].[Sales Rep].[All]" allUniqueName="[Table1].[Sales Rep].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Total2]" caption="Total2" attribute="1" defaultMemberUniqueName="[Table1].[Total2].[All]" allUniqueName="[Table1].[Total2].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Table1].[Month].[All]" allUniqueName="[Table1].[Month].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Table1].[Year].[All]" allUniqueName="[Table1].[Year].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Target]" caption="Target" attribute="1" defaultMemberUniqueName="[Table1].[Target].[All]" allUniqueName="[Table1].[Target].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Sales Rep]" caption="Sales Rep" attribute="1" defaultMemberUniqueName="[Table1].[Sales Rep].[All]" allUniqueName="[Table1].[Sales Rep].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Total2]" caption="Total2" attribute="1" defaultMemberUniqueName="[Table1].[Total2].[All]" allUniqueName="[Table1].[Total2].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Month]" caption="Month" attribute="1" defaultMemberUniqueName="[Table1].[Month].[All]" allUniqueName="[Table1].[Month].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Year]" caption="Year" attribute="1" defaultMemberUniqueName="[Table1].[Year].[All]" allUniqueName="[Table1].[Year].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Target]" caption="Target" attribute="1" defaultMemberUniqueName="[Table1].[Target].[All]" allUniqueName="[Table1].[Target].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Order Date (Year)]" caption="Order Date (Year)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Year)].[All]" allUniqueName="[Table1].[Order Date (Year)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
       <fieldsUsage count="2">
         <fieldUsage x="-1"/>
@@ -11056,7 +11197,7 @@
         <fieldUsage x="1"/>
       </fieldsUsage>
     </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Table1].[Order Date (Month Index)]" caption="Order Date (Month Index)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Month Index)].[All]" allUniqueName="[Table1].[Order Date (Month Index)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Table1].[Order Date (Month Index)]" caption="Order Date (Month Index)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Month Index)].[All]" allUniqueName="[Table1].[Order Date (Month Index)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0" hidden="1"/>
     <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
     <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
     <cacheHierarchy uniqueName="[Measures].[Sum of Quantity]" caption="Sum of Quantity" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
@@ -11096,35 +11237,25 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="mohamed elzaghal" refreshedDate="45869.426255439816" backgroundQuery="1" createdVersion="7" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{BFA525EC-1F04-4BCF-92AE-E2F1315D5C75}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="2">
-    <cacheField name="[Table1].[Product].[Product]" caption="Product" numFmtId="0" hierarchy="3" level="1">
-      <sharedItems count="5">
-        <s v="Dress"/>
-        <s v="Hat"/>
-        <s v="Jacket"/>
-        <s v="Scarf"/>
-        <s v="Sneakers"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="[Measures].[Sum of Quantity]" caption="Sum of Quantity" numFmtId="0" hierarchy="20" level="32767"/>
-  </cacheFields>
+<file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="mohamed elzaghal" refreshedDate="45871.142039467595" backgroundQuery="1" createdVersion="3" refreshedVersion="7" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{04F4D144-205A-4C91-9A85-62193B02CAC3}">
+  <cacheSource type="external" connectionId="1">
+    <extLst>
+      <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{F057638F-6D5F-4e77-A914-E7F072B9BCA8}">
+        <x14:sourceConnection name="ThisWorkbookDataModel"/>
+      </ext>
+    </extLst>
+  </cacheSource>
+  <cacheFields count="0"/>
   <cacheHierarchies count="22">
     <cacheHierarchy uniqueName="[Table1].[Order ID]" caption="Order ID" attribute="1" defaultMemberUniqueName="[Table1].[Order ID].[All]" allUniqueName="[Table1].[Order ID].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Customer]" caption="Customer" attribute="1" defaultMemberUniqueName="[Table1].[Customer].[All]" allUniqueName="[Table1].[Customer].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Customer]" caption="Customer" attribute="1" defaultMemberUniqueName="[Table1].[Customer].[All]" allUniqueName="[Table1].[Customer].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Region]" caption="Region" attribute="1" defaultMemberUniqueName="[Table1].[Region].[All]" allUniqueName="[Table1].[Region].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Table1].[Product].[All]" allUniqueName="[Table1].[Product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Table1].[Product]" caption="Product" attribute="1" defaultMemberUniqueName="[Table1].[Product].[All]" allUniqueName="[Table1].[Product].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Category]" caption="Category" attribute="1" defaultMemberUniqueName="[Table1].[Category].[All]" allUniqueName="[Table1].[Category].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Quantity]" caption="Quantity" attribute="1" defaultMemberUniqueName="[Table1].[Quantity].[All]" allUniqueName="[Table1].[Quantity].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Unit Price]" caption="Unit Price" attribute="1" defaultMemberUniqueName="[Table1].[Unit Price].[All]" allUniqueName="[Table1].[Unit Price].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Table1].[Total]" caption="Total" attribute="1" defaultMemberUniqueName="[Table1].[Total].[All]" allUniqueName="[Table1].[Total].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Table1].[Total]" caption="Total" attribute="1" defaultMemberUniqueName="[Table1].[Total].[All]" allUniqueName="[Table1].[Total].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="2" memberValueDatatype="5" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Order Date]" caption="Order Date" attribute="1" time="1" defaultMemberUniqueName="[Table1].[Order Date].[All]" allUniqueName="[Table1].[Order Date].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="7" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Sales Rep]" caption="Sales Rep" attribute="1" defaultMemberUniqueName="[Table1].[Sales Rep].[All]" allUniqueName="[Table1].[Sales Rep].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Table1].[Total2]" caption="Total2" attribute="1" defaultMemberUniqueName="[Table1].[Total2].[All]" allUniqueName="[Table1].[Total2].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
@@ -11137,10 +11268,7 @@
     <cacheHierarchy uniqueName="[Table1].[Order Date (Month Index)]" caption="Order Date (Month Index)" attribute="1" defaultMemberUniqueName="[Table1].[Order Date (Month Index)].[All]" allUniqueName="[Table1].[Order Date (Month Index)].[All]" dimensionUniqueName="[Table1]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0" hidden="1"/>
     <cacheHierarchy uniqueName="[Measures].[__XL_Count Table1]" caption="__XL_Count Table1" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1"/>
     <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Quantity]" caption="Sum of Quantity" measure="1" displayFolder="" measureGroup="Table1" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Quantity]" caption="Sum of Quantity" measure="1" displayFolder="" measureGroup="Table1" count="0" hidden="1">
       <extLst>
         <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
           <x15:cacheHierarchy aggregatedColumn="5"/>
@@ -11156,28 +11284,18 @@
     </cacheHierarchy>
   </cacheHierarchies>
   <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Table1" uniqueName="[Table1]" caption="Table1"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Table1" caption="Table1"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+      <x14:pivotCacheDefinition slicerData="1" pivotCacheId="644539996" supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
     </ext>
   </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC969D65-E2CE-480C-BD65-F7E2476837E7}" name="Sales Anlysis by seller" cacheId="42" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FC969D65-E2CE-480C-BD65-F7E2476837E7}" name="Sales Anlysis by seller" cacheId="53" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="B3:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
+  <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="5">
         <item x="0"/>
@@ -11188,6 +11306,7 @@
       </items>
     </pivotField>
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
@@ -11219,7 +11338,7 @@
     <dataField name="Sum of Total" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="0">
+    <format dxfId="2">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
@@ -11249,7 +11368,7 @@
   </chartFormats>
   <pivotHierarchies count="22">
     <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -11292,9 +11411,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E9DBBF7-73F7-4DF5-BD2F-00065CB51A51}" name="Sales Anlysis by month" cacheId="96" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3E9DBBF7-73F7-4DF5-BD2F-00065CB51A51}" name="Sales Anlysis by month" cacheId="56" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="B2:C20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="5">
+  <pivotFields count="6">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="15">
         <item x="0"/>
@@ -11339,6 +11458,7 @@
       </items>
     </pivotField>
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
   </pivotFields>
   <rowFields count="4">
     <field x="3"/>
@@ -11430,7 +11550,7 @@
   </chartFormats>
   <pivotHierarchies count="22">
     <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -11476,9 +11596,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5299B2AC-E51C-4FA8-8778-1025F6D86719}" name="Sales Anlysis by category" cacheId="45" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{5299B2AC-E51C-4FA8-8778-1025F6D86719}" name="Sales Anlysis by category" cacheId="49" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
   <location ref="B2:C6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
+  <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="3">
         <item x="0"/>
@@ -11487,6 +11607,7 @@
       </items>
     </pivotField>
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
@@ -11512,7 +11633,7 @@
     <dataField name="Sum of Total" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="1">
-    <format dxfId="1">
+    <format dxfId="3">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
@@ -11569,7 +11690,7 @@
   </chartFormats>
   <pivotHierarchies count="22">
     <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -11612,9 +11733,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FD203AE-5739-4E81-870B-7074040B08F8}" name="Sales Anlysis by product" cacheId="99" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{8FD203AE-5739-4E81-870B-7074040B08F8}" name="Sales Anlysis by product" cacheId="51" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="7" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="7" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="B3:C9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="2">
+  <pivotFields count="3">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" sortType="ascending" defaultSubtotal="0" defaultAttributeDrillState="1">
       <items count="5">
         <item x="0"/>
@@ -11625,6 +11746,7 @@
       </items>
     </pivotField>
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
@@ -11655,7 +11777,7 @@
   <dataFields count="1">
     <dataField name="Sum of Quantity" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="8">
+  <chartFormats count="13">
     <chartFormat chart="1" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -11743,10 +11865,70 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="2" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotHierarchies count="22">
     <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -11788,24 +11970,112 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Customer" xr10:uid="{470D3755-EC0A-4EEB-8261-D9B506EBDD8F}" sourceName="[Table1].[Customer]">
+  <pivotTables>
+    <pivotTable tabId="7" name="Sales Anlysis by month"/>
+    <pivotTable tabId="5" name="Sales Anlysis by category"/>
+    <pivotTable tabId="3" name="Sales Anlysis by product"/>
+    <pivotTable tabId="6" name="Sales Anlysis by seller"/>
+  </pivotTables>
+  <data>
+    <olap pivotCacheId="644539996">
+      <levels count="2">
+        <level uniqueName="[Table1].[Customer].[(All)]" sourceCaption="(All)" count="0"/>
+        <level uniqueName="[Table1].[Customer].[Customer]" sourceCaption="Customer" count="15">
+          <ranges>
+            <range startItem="0">
+              <i n="[Table1].[Customer].&amp;[Brady Miles]" c="Brady Miles"/>
+              <i n="[Table1].[Customer].&amp;[Cole Cline]" c="Cole Cline"/>
+              <i n="[Table1].[Customer].&amp;[David George]" c="David George"/>
+              <i n="[Table1].[Customer].&amp;[Halk]" c="Halk"/>
+              <i n="[Table1].[Customer].&amp;[Jack Dosen]" c="Jack Dosen"/>
+              <i n="[Table1].[Customer].&amp;[Jessica Pierce]" c="Jessica Pierce"/>
+              <i n="[Table1].[Customer].&amp;[Kimberly Jones]" c="Kimberly Jones"/>
+              <i n="[Table1].[Customer].&amp;[Manuel Guerra]" c="Manuel Guerra"/>
+              <i n="[Table1].[Customer].&amp;[Michael Allen]" c="Michael Allen"/>
+              <i n="[Table1].[Customer].&amp;[Michelle Ferguson]" c="Michelle Ferguson"/>
+              <i n="[Table1].[Customer].&amp;[Misty Huber]" c="Misty Huber"/>
+              <i n="[Table1].[Customer].&amp;[Mrs. Samantha Newton]" c="Mrs. Samantha Newton"/>
+              <i n="[Table1].[Customer].&amp;[Paper starck]" c="Paper starck"/>
+              <i n="[Table1].[Customer].&amp;[Rose]" c="Rose"/>
+              <i n="[Table1].[Customer].&amp;[Tony Starck]" c="Tony Starck"/>
+            </range>
+          </ranges>
+        </level>
+      </levels>
+      <selections count="1">
+        <selection n="[Table1].[Customer].[All]"/>
+      </selections>
+    </olap>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Total" xr10:uid="{BE74B1A6-2FAB-4876-A1FC-143E774DC659}" sourceName="[Table1].[Total]">
+  <pivotTables>
+    <pivotTable tabId="7" name="Sales Anlysis by month"/>
+  </pivotTables>
+  <data>
+    <olap pivotCacheId="644539996">
+      <levels count="2">
+        <level uniqueName="[Table1].[Total].[(All)]" sourceCaption="(All)" count="0"/>
+        <level uniqueName="[Table1].[Total].[Total]" sourceCaption="Total" count="15">
+          <ranges>
+            <range startItem="0">
+              <i n="[Table1].[Total].&amp;[2.212E2]" c="221.2"/>
+              <i n="[Table1].[Total].&amp;[2.8818E2]" c="288.18"/>
+              <i n="[Table1].[Total].&amp;[8.7102E2]" c="871.02"/>
+              <i n="[Table1].[Total].&amp;[1.03796E3]" c="1037.96"/>
+              <i n="[Table1].[Total].&amp;[1.12194E3]" c="1121.94"/>
+              <i n="[Table1].[Total].&amp;[1.26216E3]" c="1262.16"/>
+              <i n="[Table1].[Total].&amp;[1.71304E3]" c="1713.04"/>
+              <i n="[Table1].[Total].&amp;[2.12582266666667E3]" c="2125.82266666667"/>
+              <i n="[Table1].[Total].&amp;[2.24243224242424E3]" c="2242.43224242424"/>
+              <i n="[Table1].[Total].&amp;[2.35904181818182E3]" c="2359.04181818182"/>
+              <i n="[Table1].[Total].&amp;[2.37366E3]" c="2373.66"/>
+              <i n="[Table1].[Total].&amp;[2.4756513939394E3]" c="2475.6513939394"/>
+              <i n="[Table1].[Total].&amp;[2.59226096969697E3]" c="2592.26096969697"/>
+              <i n="[Table1].[Total].&amp;[2.70384E3]" c="2703.84"/>
+              <i n="[Table1].[Total].&amp;[3.2517E3]" c="3251.7"/>
+            </range>
+          </ranges>
+        </level>
+      </levels>
+      <selections count="1">
+        <selection n="[Table1].[Total].[All]"/>
+      </selections>
+    </olap>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Customer" xr10:uid="{1828DACD-4676-49A8-A144-449746F2EF8A}" cache="Slicer_Customer" caption="Customer" level="1" rowHeight="241300"/>
+  <slicer name="Total" xr10:uid="{BF16907A-F665-4836-B1C0-FC8653888F73}" cache="Slicer_Total" caption="Total" level="1" rowHeight="241300"/>
+</slicers>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D6E7092-2E04-4E3D-BF21-62E6A2CD7CC2}" name="Table1" displayName="Table1" ref="C3:P18" totalsRowShown="0" headerRowDxfId="20" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5D6E7092-2E04-4E3D-BF21-62E6A2CD7CC2}" name="Table1" displayName="Table1" ref="C3:P18" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="C3:P18" xr:uid="{5D6E7092-2E04-4E3D-BF21-62E6A2CD7CC2}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{B217AE02-CA6E-47E5-AA55-BEAC0D4F3E64}" name="Order ID" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{B3FF03E4-8644-4D51-BEFD-5F431987D9E5}" name="Customer" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{E949FA20-939F-4832-A189-8DC8F05470B8}" name="Region" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{4D4C373B-A1AC-44C9-A03A-38A72D3C0218}" name="Product" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{436BD014-8AF8-4220-82D0-CCC71B20E0EA}" name="Category" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{ED42FF88-3B7F-49ED-8B98-21D3819F10A7}" name="Quantity" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{B14C1E70-0D4F-4D38-B089-05A1AE5247F7}" name="Unit Price" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{9B190FA4-B7FB-457F-93F3-8E34E125FF5B}" name="Total" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{42B80C4B-C7D5-4BE0-89DF-61DA442B87E5}" name="Order Date" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{81D36830-807C-420F-8D65-39B4F9E906DB}" name="Sales Rep" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{DCDF4310-1305-4A3C-A286-51518DE08084}" name="Total2" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{B217AE02-CA6E-47E5-AA55-BEAC0D4F3E64}" name="Order ID" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{B3FF03E4-8644-4D51-BEFD-5F431987D9E5}" name="Customer" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{E949FA20-939F-4832-A189-8DC8F05470B8}" name="Region" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{4D4C373B-A1AC-44C9-A03A-38A72D3C0218}" name="Product" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{436BD014-8AF8-4220-82D0-CCC71B20E0EA}" name="Category" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{ED42FF88-3B7F-49ED-8B98-21D3819F10A7}" name="Quantity" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{B14C1E70-0D4F-4D38-B089-05A1AE5247F7}" name="Unit Price" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{9B190FA4-B7FB-457F-93F3-8E34E125FF5B}" name="Total" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{42B80C4B-C7D5-4BE0-89DF-61DA442B87E5}" name="Order Date" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{81D36830-807C-420F-8D65-39B4F9E906DB}" name="Sales Rep" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{DCDF4310-1305-4A3C-A286-51518DE08084}" name="Total2" dataDxfId="14">
       <calculatedColumnFormula>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{BD4055FD-E78C-4E0F-9358-18A8F41290C7}" name="Month " dataDxfId="3">
+    <tableColumn id="12" xr3:uid="{BD4055FD-E78C-4E0F-9358-18A8F41290C7}" name="Month " dataDxfId="13">
       <calculatedColumnFormula>MONTH(Table1[[#This Row],[Order Date]])</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="13" xr3:uid="{A46D920F-E10A-40FD-8B3B-6DBC1F9EBA02}" name="Year" dataDxfId="12">
@@ -12106,22 +12376,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-      <c r="N1" s="5"/>
-      <c r="O1" s="5"/>
-      <c r="P1" s="5"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
     </row>
     <row r="2" spans="3:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="3:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -12190,7 +12460,7 @@
       <c r="I4" s="3">
         <v>373.98</v>
       </c>
-      <c r="J4" s="9">
+      <c r="J4" s="8">
         <v>1121.94</v>
       </c>
       <c r="K4" s="4">
@@ -12199,7 +12469,7 @@
       <c r="L4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M4" s="10">
+      <c r="M4" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>1121.94</v>
       </c>
@@ -12238,7 +12508,7 @@
       <c r="I5" s="3">
         <v>96.06</v>
       </c>
-      <c r="J5" s="9">
+      <c r="J5" s="8">
         <v>288.18</v>
       </c>
       <c r="K5" s="4">
@@ -12247,7 +12517,7 @@
       <c r="L5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>288.18</v>
       </c>
@@ -12286,7 +12556,7 @@
       <c r="I6" s="3">
         <v>214.13</v>
       </c>
-      <c r="J6" s="9">
+      <c r="J6" s="8">
         <v>1713.04</v>
       </c>
       <c r="K6" s="4">
@@ -12295,7 +12565,7 @@
       <c r="L6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>1713.04</v>
       </c>
@@ -12334,7 +12604,7 @@
       <c r="I7" s="3">
         <v>395.61</v>
       </c>
-      <c r="J7" s="9">
+      <c r="J7" s="8">
         <v>2373.66</v>
       </c>
       <c r="K7" s="4">
@@ -12343,7 +12613,7 @@
       <c r="L7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>2373.66</v>
       </c>
@@ -12382,7 +12652,7 @@
       <c r="I8" s="3">
         <v>259.49</v>
       </c>
-      <c r="J8" s="9">
+      <c r="J8" s="8">
         <v>1037.96</v>
       </c>
       <c r="K8" s="4">
@@ -12391,7 +12661,7 @@
       <c r="L8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M8" s="10">
+      <c r="M8" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>1037.96</v>
       </c>
@@ -12430,7 +12700,7 @@
       <c r="I9" s="3">
         <v>96.78</v>
       </c>
-      <c r="J9" s="9">
+      <c r="J9" s="8">
         <v>871.02</v>
       </c>
       <c r="K9" s="4">
@@ -12439,7 +12709,7 @@
       <c r="L9" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>871.02</v>
       </c>
@@ -12478,7 +12748,7 @@
       <c r="I10" s="3">
         <v>55.3</v>
       </c>
-      <c r="J10" s="9">
+      <c r="J10" s="8">
         <v>221.2</v>
       </c>
       <c r="K10" s="4">
@@ -12487,7 +12757,7 @@
       <c r="L10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>221.2</v>
       </c>
@@ -12526,7 +12796,7 @@
       <c r="I11" s="3">
         <v>325.17</v>
       </c>
-      <c r="J11" s="9">
+      <c r="J11" s="8">
         <v>3251.7</v>
       </c>
       <c r="K11" s="4">
@@ -12535,7 +12805,7 @@
       <c r="L11" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>3251.7000000000003</v>
       </c>
@@ -12574,7 +12844,7 @@
       <c r="I12" s="3">
         <v>337.98</v>
       </c>
-      <c r="J12" s="9">
+      <c r="J12" s="8">
         <v>2703.84</v>
       </c>
       <c r="K12" s="4">
@@ -12583,7 +12853,7 @@
       <c r="L12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M12" s="10">
+      <c r="M12" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>2703.84</v>
       </c>
@@ -12622,7 +12892,7 @@
       <c r="I13" s="3">
         <v>233.29222222222199</v>
       </c>
-      <c r="J13" s="9">
+      <c r="J13" s="8">
         <v>1262.1600000000001</v>
       </c>
       <c r="K13" s="4">
@@ -12631,7 +12901,7 @@
       <c r="L13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M13" s="10">
+      <c r="M13" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>2099.6299999999978</v>
       </c>
@@ -12670,7 +12940,7 @@
       <c r="I14" s="3">
         <v>232.072888888889</v>
       </c>
-      <c r="J14" s="9">
+      <c r="J14" s="8">
         <v>2125.8226666666701</v>
       </c>
       <c r="K14" s="4">
@@ -12679,7 +12949,7 @@
       <c r="L14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M14" s="10">
+      <c r="M14" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>1624.5102222222231</v>
       </c>
@@ -12718,7 +12988,7 @@
       <c r="I15" s="3">
         <v>230.853555555556</v>
       </c>
-      <c r="J15" s="9">
+      <c r="J15" s="8">
         <v>2242.43224242424</v>
       </c>
       <c r="K15" s="4">
@@ -12727,7 +12997,7 @@
       <c r="L15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="10">
+      <c r="M15" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>1154.2677777777799</v>
       </c>
@@ -12766,7 +13036,7 @@
       <c r="I16" s="3">
         <v>229.63422222222201</v>
       </c>
-      <c r="J16" s="9">
+      <c r="J16" s="8">
         <v>2359.04181818182</v>
       </c>
       <c r="K16" s="4">
@@ -12775,7 +13045,7 @@
       <c r="L16" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>2755.6106666666642</v>
       </c>
@@ -12814,7 +13084,7 @@
       <c r="I17" s="3">
         <v>228.41488888888901</v>
       </c>
-      <c r="J17" s="9">
+      <c r="J17" s="8">
         <v>2475.6513939393999</v>
       </c>
       <c r="K17" s="4">
@@ -12823,7 +13093,7 @@
       <c r="L17" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M17" s="10">
+      <c r="M17" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>3426.2233333333352</v>
       </c>
@@ -12862,7 +13132,7 @@
       <c r="I18" s="3">
         <v>227.19555555555601</v>
       </c>
-      <c r="J18" s="9">
+      <c r="J18" s="8">
         <v>2592.2609696969698</v>
       </c>
       <c r="K18" s="4">
@@ -12871,7 +13141,7 @@
       <c r="L18" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="9">
         <f>Table1[[#This Row],[Quantity]]*Table1[[#This Row],[Unit Price]]</f>
         <v>4089.5200000000082</v>
       </c>
@@ -12967,7 +13237,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
@@ -12975,50 +13245,50 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>3401.6322424242398</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>2703.84</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C6" s="10">
         <v>7099.1836363636394</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>3251.7</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="10">
         <v>10183.55321212122</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>26639.909090909096</v>
       </c>
     </row>
@@ -13041,7 +13311,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
@@ -13049,134 +13319,134 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C3" s="8"/>
+      <c r="C3" s="7"/>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="8"/>
+      <c r="C4" s="7"/>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>1121.94</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>288.18</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C7" s="8"/>
+      <c r="C7" s="7"/>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>1713.04</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>2373.66</v>
       </c>
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="7">
         <v>1037.96</v>
       </c>
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B11" s="12" t="s">
+      <c r="B11" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C11" s="7">
         <v>4343.92</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="8"/>
+      <c r="C12" s="7"/>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="11" t="s">
         <v>76</v>
       </c>
-      <c r="C13" s="8">
+      <c r="C13" s="7">
         <v>6091.8226666666706</v>
       </c>
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="8"/>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="7">
         <v>2242.43224242424</v>
       </c>
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="7">
         <v>2359.04181818182</v>
       </c>
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="8">
+      <c r="C17" s="7">
         <v>2475.6513939393999</v>
       </c>
     </row>
     <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="12" t="s">
+      <c r="B18" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="C18" s="8"/>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="7">
         <v>2592.2609696969698</v>
       </c>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="7">
         <v>26639.909090909096</v>
       </c>
     </row>
@@ -13199,7 +13469,7 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C2" t="s">
@@ -13207,34 +13477,34 @@
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>11285.844484848491</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="10">
         <v>4343.92</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>11010.14460606061</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>26639.909090909096</v>
       </c>
     </row>
@@ -13248,12 +13518,52 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC0004C2-4009-4BDA-9DAA-96ED205FA85E}">
   <sheetPr>
     <tabColor theme="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <sheetData>
+    <row r="1" spans="1:22" ht="3" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="1:22" ht="50.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+      <c r="R2" s="14"/>
+      <c r="S2" s="14"/>
+      <c r="T2" s="14"/>
+      <c r="U2" s="14"/>
+      <c r="V2" s="14"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:V2"/>
+  </mergeCells>
+  <pageMargins left="1" right="1.75" top="4.75" bottom="0" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="2" scale="28" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
@@ -13270,7 +13580,7 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>62</v>
       </c>
       <c r="C3" t="s">
@@ -13278,50 +13588,50 @@
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="7">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="7">
         <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="7">
         <v>9</v>
       </c>
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="7">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="7">
         <v>51</v>
       </c>
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="7">
         <v>121</v>
       </c>
     </row>
